--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>121370417</v>
       </c>
       <c r="B11" t="n">
-        <v>98097</v>
+        <v>98107</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121366898</v>
+        <v>121368730</v>
       </c>
       <c r="B12" t="n">
-        <v>98056</v>
+        <v>99120</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219799</v>
+        <v>222662</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121367144</v>
+        <v>121366898</v>
       </c>
       <c r="B13" t="n">
-        <v>98002</v>
+        <v>98066</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219794</v>
+        <v>219799</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
         <v>121367464</v>
       </c>
       <c r="B14" t="n">
-        <v>97979</v>
+        <v>97989</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>121369139</v>
       </c>
       <c r="B15" t="n">
-        <v>105075</v>
+        <v>105085</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121368730</v>
+        <v>121367144</v>
       </c>
       <c r="B16" t="n">
-        <v>99110</v>
+        <v>98012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222662</v>
+        <v>219794</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121370417</v>
+        <v>121368730</v>
       </c>
       <c r="B11" t="n">
-        <v>98107</v>
+        <v>99120</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,16 +1699,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222118</v>
+        <v>222662</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121368730</v>
+        <v>121370417</v>
       </c>
       <c r="B12" t="n">
-        <v>99120</v>
+        <v>98107</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,16 +1802,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222662</v>
+        <v>222118</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121368730</v>
+        <v>121367144</v>
       </c>
       <c r="B11" t="n">
-        <v>99120</v>
+        <v>98012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222662</v>
+        <v>219794</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121366898</v>
+        <v>121368730</v>
       </c>
       <c r="B13" t="n">
-        <v>98066</v>
+        <v>99120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219799</v>
+        <v>222662</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121367464</v>
+        <v>121366898</v>
       </c>
       <c r="B14" t="n">
-        <v>97989</v>
+        <v>98066</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,21 +2008,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219788</v>
+        <v>219799</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121369139</v>
+        <v>121367464</v>
       </c>
       <c r="B15" t="n">
-        <v>105085</v>
+        <v>97989</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,25 +2107,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221137</v>
+        <v>219788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121367144</v>
+        <v>121369139</v>
       </c>
       <c r="B16" t="n">
-        <v>98012</v>
+        <v>105085</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,25 +2210,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219794</v>
+        <v>221137</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367144</v>
+        <v>121366898</v>
       </c>
       <c r="B11" t="n">
-        <v>98012</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219794</v>
+        <v>219799</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121370417</v>
+        <v>121367464</v>
       </c>
       <c r="B12" t="n">
-        <v>98107</v>
+        <v>98002</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222118</v>
+        <v>219788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121368730</v>
+        <v>121370417</v>
       </c>
       <c r="B13" t="n">
-        <v>99120</v>
+        <v>98120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222662</v>
+        <v>222118</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121366898</v>
+        <v>121369139</v>
       </c>
       <c r="B14" t="n">
-        <v>98066</v>
+        <v>105098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,25 +2004,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219799</v>
+        <v>221137</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121367464</v>
+        <v>121367144</v>
       </c>
       <c r="B15" t="n">
-        <v>97989</v>
+        <v>98025</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219788</v>
+        <v>219794</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121369139</v>
+        <v>121368730</v>
       </c>
       <c r="B16" t="n">
-        <v>105085</v>
+        <v>99133</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221137</v>
+        <v>222662</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121366898</v>
+        <v>121370417</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>98121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219799</v>
+        <v>222118</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367464</v>
+        <v>121369139</v>
       </c>
       <c r="B12" t="n">
-        <v>98002</v>
+        <v>105099</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,25 +1798,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219788</v>
+        <v>221137</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121370417</v>
+        <v>121367144</v>
       </c>
       <c r="B13" t="n">
-        <v>98120</v>
+        <v>98026</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222118</v>
+        <v>219794</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121369139</v>
+        <v>121368730</v>
       </c>
       <c r="B14" t="n">
-        <v>105098</v>
+        <v>99134</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,20 +2004,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221137</v>
+        <v>222662</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121367144</v>
+        <v>121366898</v>
       </c>
       <c r="B15" t="n">
-        <v>98025</v>
+        <v>98080</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219794</v>
+        <v>219799</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121368730</v>
+        <v>121367464</v>
       </c>
       <c r="B16" t="n">
-        <v>99133</v>
+        <v>98003</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121370417</v>
+        <v>121367464</v>
       </c>
       <c r="B11" t="n">
-        <v>98121</v>
+        <v>98006</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222118</v>
+        <v>219788</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>121369139</v>
       </c>
       <c r="B12" t="n">
-        <v>105099</v>
+        <v>105102</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>121367144</v>
       </c>
       <c r="B13" t="n">
-        <v>98026</v>
+        <v>98029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121368730</v>
+        <v>121370417</v>
       </c>
       <c r="B14" t="n">
-        <v>99134</v>
+        <v>98124</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,16 +2008,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222662</v>
+        <v>222118</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2098,7 +2098,7 @@
         <v>121366898</v>
       </c>
       <c r="B15" t="n">
-        <v>98080</v>
+        <v>98083</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121367464</v>
+        <v>121368730</v>
       </c>
       <c r="B16" t="n">
-        <v>98003</v>
+        <v>99137</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121369139</v>
+        <v>121370417</v>
       </c>
       <c r="B12" t="n">
-        <v>105102</v>
+        <v>98124</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,20 +1798,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221137</v>
+        <v>222118</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121367144</v>
+        <v>121368730</v>
       </c>
       <c r="B13" t="n">
-        <v>98029</v>
+        <v>99137</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219794</v>
+        <v>222662</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121370417</v>
+        <v>121367144</v>
       </c>
       <c r="B14" t="n">
-        <v>98124</v>
+        <v>98029</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,21 +2008,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222118</v>
+        <v>219794</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121368730</v>
+        <v>121369139</v>
       </c>
       <c r="B16" t="n">
-        <v>99137</v>
+        <v>105102</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222662</v>
+        <v>221137</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367464</v>
+        <v>121366898</v>
       </c>
       <c r="B11" t="n">
-        <v>98006</v>
+        <v>98089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219788</v>
+        <v>219799</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121370417</v>
+        <v>121367144</v>
       </c>
       <c r="B12" t="n">
-        <v>98124</v>
+        <v>98035</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222118</v>
+        <v>219794</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121368730</v>
+        <v>121367464</v>
       </c>
       <c r="B13" t="n">
-        <v>99137</v>
+        <v>98012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121367144</v>
+        <v>121370417</v>
       </c>
       <c r="B14" t="n">
-        <v>98029</v>
+        <v>98130</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,21 +2008,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219794</v>
+        <v>222118</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121366898</v>
+        <v>121369139</v>
       </c>
       <c r="B15" t="n">
-        <v>98083</v>
+        <v>105108</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,25 +2107,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219799</v>
+        <v>221137</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121369139</v>
+        <v>121368730</v>
       </c>
       <c r="B16" t="n">
-        <v>105102</v>
+        <v>99143</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,20 +2210,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221137</v>
+        <v>222662</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121366898</v>
+        <v>121370417</v>
       </c>
       <c r="B11" t="n">
-        <v>98089</v>
+        <v>98131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219799</v>
+        <v>222118</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367144</v>
+        <v>121368730</v>
       </c>
       <c r="B12" t="n">
-        <v>98035</v>
+        <v>99144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219794</v>
+        <v>222662</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1892,7 +1892,7 @@
         <v>121367464</v>
       </c>
       <c r="B13" t="n">
-        <v>98012</v>
+        <v>98013</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121370417</v>
+        <v>121367144</v>
       </c>
       <c r="B14" t="n">
-        <v>98130</v>
+        <v>98036</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,21 +2008,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222118</v>
+        <v>219794</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
         <v>121369139</v>
       </c>
       <c r="B15" t="n">
-        <v>105108</v>
+        <v>105109</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121368730</v>
+        <v>121366898</v>
       </c>
       <c r="B16" t="n">
-        <v>99143</v>
+        <v>98090</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222662</v>
+        <v>219799</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121370417</v>
+        <v>121369139</v>
       </c>
       <c r="B11" t="n">
-        <v>98131</v>
+        <v>105109</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,20 +1695,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222118</v>
+        <v>221137</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121368730</v>
+        <v>121367144</v>
       </c>
       <c r="B12" t="n">
-        <v>99144</v>
+        <v>98036</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222662</v>
+        <v>219794</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121367464</v>
+        <v>121370417</v>
       </c>
       <c r="B13" t="n">
-        <v>98013</v>
+        <v>98131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219788</v>
+        <v>222118</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121367144</v>
+        <v>121366898</v>
       </c>
       <c r="B14" t="n">
-        <v>98036</v>
+        <v>98090</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,21 +2008,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219794</v>
+        <v>219799</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121369139</v>
+        <v>121368730</v>
       </c>
       <c r="B15" t="n">
-        <v>105109</v>
+        <v>99144</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,20 +2107,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221137</v>
+        <v>222662</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121366898</v>
+        <v>121367464</v>
       </c>
       <c r="B16" t="n">
-        <v>98090</v>
+        <v>98013</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219799</v>
+        <v>219788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367144</v>
+        <v>121368730</v>
       </c>
       <c r="B12" t="n">
-        <v>98036</v>
+        <v>99144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219794</v>
+        <v>222662</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121366898</v>
+        <v>121367144</v>
       </c>
       <c r="B14" t="n">
-        <v>98090</v>
+        <v>98036</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,21 +2008,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219799</v>
+        <v>219794</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121368730</v>
+        <v>121367464</v>
       </c>
       <c r="B15" t="n">
-        <v>99144</v>
+        <v>98013</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121367464</v>
+        <v>121366898</v>
       </c>
       <c r="B16" t="n">
-        <v>98013</v>
+        <v>98090</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219788</v>
+        <v>219799</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 44916-2022 artfynd.xlsx
+++ b/artfynd/A 44916-2022 artfynd.xlsx
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121369139</v>
+        <v>121367144</v>
       </c>
       <c r="B11" t="n">
-        <v>105109</v>
+        <v>98036</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221137</v>
+        <v>219794</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121368730</v>
+        <v>121367464</v>
       </c>
       <c r="B12" t="n">
-        <v>99144</v>
+        <v>98013</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121370417</v>
+        <v>121369139</v>
       </c>
       <c r="B13" t="n">
-        <v>98131</v>
+        <v>105109</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,20 +1901,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222118</v>
+        <v>221137</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1992,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121367144</v>
+        <v>121370417</v>
       </c>
       <c r="B14" t="n">
-        <v>98036</v>
+        <v>98131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,21 +2008,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219794</v>
+        <v>222118</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121367464</v>
+        <v>121366898</v>
       </c>
       <c r="B15" t="n">
-        <v>98013</v>
+        <v>98090</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219788</v>
+        <v>219799</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121366898</v>
+        <v>121368730</v>
       </c>
       <c r="B16" t="n">
-        <v>98090</v>
+        <v>99144</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219799</v>
+        <v>222662</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
